--- a/results/Int Task Remove ACC -0.0/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.0/Rando_9_permute.xlsx
@@ -440,647 +440,647 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7483772087991345</v>
+        <v>0.7262527046520015</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7561346015146051</v>
+        <v>0.7262592408943382</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7661929769203029</v>
+        <v>0.7262592408943382</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7661929769203029</v>
+        <v>0.7246100793364587</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7665319599711504</v>
+        <v>0.7272957987738911</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7519631265777136</v>
+        <v>0.7394207536963577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7400996213487199</v>
+        <v>0.702105571583123</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7483911828344753</v>
+        <v>0.7017404435629282</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7506865308330328</v>
+        <v>0.6711300937612694</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.757707131265777</v>
+        <v>0.6718276685899747</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7466710241615578</v>
+        <v>0.6718276685899747</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7406412279120087</v>
+        <v>0.6695070771727372</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7412930490443563</v>
+        <v>0.6358711233321312</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7192095654525784</v>
+        <v>0.6228347006851784</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7202265146051208</v>
+        <v>0.6295359267940859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7167647854309412</v>
+        <v>0.6305267309772808</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7221427605481427</v>
+        <v>0.634463802740714</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6916034078615219</v>
+        <v>0.6213097277316986</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.685951812116841</v>
+        <v>0.6304622701045799</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6798949693472773</v>
+        <v>0.6304622701045799</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7023136043995672</v>
+        <v>0.6321628200504869</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6718256401009737</v>
+        <v>0.6506761630003606</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6635929047962495</v>
+        <v>0.6513214478903715</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6654764695275874</v>
+        <v>0.6336420393076091</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6576798593580959</v>
+        <v>0.6416861251352326</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.644354940497656</v>
+        <v>0.6424033086909484</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.62015641904075</v>
+        <v>0.6348999278759466</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.62015641904075</v>
+        <v>0.5888009376126938</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6315716282005048</v>
+        <v>0.5884684908041832</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6198183375405698</v>
+        <v>0.6084806617381897</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6123663451135954</v>
+        <v>0.5545057248467364</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6365256491164804</v>
+        <v>0.551748106743599</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6382336368553913</v>
+        <v>0.5440233952398125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6309908041831951</v>
+        <v>0.5398388478182474</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6246612423368194</v>
+        <v>0.5409146231518212</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6422099260728453</v>
+        <v>0.5198510187522539</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6896657500901551</v>
+        <v>0.5208875766318066</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6933553461954562</v>
+        <v>0.5249815182113234</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6933488099531193</v>
+        <v>0.5236190497655968</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6653457446808511</v>
+        <v>0.5232800667147494</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6653326721961774</v>
+        <v>0.5216252704652001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6586902722683015</v>
+        <v>0.5722784439235485</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6512745672556798</v>
+        <v>0.5614122791200865</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6578450685178507</v>
+        <v>0.5537128110349802</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6602048773891093</v>
+        <v>0.5582307068157231</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6175545438153625</v>
+        <v>0.5402655066714749</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5888212225027046</v>
+        <v>0.5427495041471331</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5888212225027046</v>
+        <v>0.5415121258564731</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5546903173458348</v>
+        <v>0.5181231968986657</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5338638207717273</v>
+        <v>0.5221208979444645</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5435178507032096</v>
+        <v>0.5264296339704292</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5491563739632167</v>
+        <v>0.508216958168049</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5508120717634331</v>
+        <v>0.5085167237648756</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5557530201947349</v>
+        <v>0.4949713757663181</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5222020375045078</v>
+        <v>0.4940001803101334</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5272214208438514</v>
+        <v>0.4894953570140642</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5019685358817165</v>
+        <v>0.4968418680129824</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5019750721240533</v>
+        <v>0.4720064010097367</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5019750721240533</v>
+        <v>0.4915236206274793</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5049670934006492</v>
+        <v>0.5062707356653444</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5026530382257482</v>
+        <v>0.5006518211323476</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5026530382257482</v>
+        <v>0.5006191399206635</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5033244680851063</v>
+        <v>0.4995825820411107</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5033244680851063</v>
+        <v>0.4995825820411107</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5026595744680851</v>
+        <v>0.4978876667868734</v>
       </c>
     </row>
     <row r="67">
@@ -1090,67 +1090,67 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5026595744680851</v>
+        <v>0.4978942030292102</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5036373061666066</v>
+        <v>0.4995695095564371</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5032787143887486</v>
+        <v>0.4979072755138839</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5032787143887486</v>
+        <v>0.4965840245221781</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5032787143887486</v>
+        <v>0.4958864496934728</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5036111611972592</v>
+        <v>0.4958864496934728</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5026138207717273</v>
+        <v>0.4969491525423729</v>
       </c>
     </row>
     <row r="74">
@@ -1160,167 +1160,167 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5026334294987379</v>
+        <v>0.4975944374323837</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5066097187161919</v>
+        <v>0.4969164713306888</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5046346465921385</v>
+        <v>0.4962450414713307</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5049801658853228</v>
+        <v>0.4952477010457988</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5076397403534079</v>
+        <v>0.4969426163000361</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5076397403534079</v>
+        <v>0.4986309953119365</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5142886765236206</v>
+        <v>0.498969978362784</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.508311170212766</v>
+        <v>0.4996348719798053</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5036046249549224</v>
+        <v>0.4993220338983051</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5036046249549224</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5036373061666066</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5006583573746844</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5009842679408583</v>
+        <v>0.4993220338983051</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5009842679408583</v>
+        <v>0.4993220338983051</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5003259105661738</v>
+        <v>0.4993220338983051</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5003324468085106</v>
+        <v>0.5003259105661738</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4996610169491525</v>
+        <v>0.4999869275153264</v>
       </c>
     </row>
   </sheetData>
